--- a/data/trans_orig/P05A02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05A02-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2007</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2007 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>741540</t>
+          <t>740097</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>794965</t>
+          <t>796098</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>938436</t>
+          <t>937406</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1001120</t>
+          <t>1002398</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1699597</t>
+          <t>1701601</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1782041</t>
+          <t>1785547</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,14%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>198645</t>
+          <t>198344</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>250949</t>
+          <t>250922</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>247970</t>
+          <t>248972</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>306364</t>
+          <t>306795</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>461090</t>
+          <t>458074</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>536522</t>
+          <t>537225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27273</t>
+          <t>28499</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51465</t>
+          <t>54179</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51479</t>
+          <t>50720</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83849</t>
+          <t>81975</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>86363</t>
+          <t>85677</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>125209</t>
+          <t>124015</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1314002</t>
+          <t>1313632</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1382173</t>
+          <t>1378955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1143114</t>
+          <t>1142538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1211662</t>
+          <t>1210186</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2476075</t>
+          <t>2473273</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2573118</t>
+          <t>2569139</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,51%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>265232</t>
+          <t>265809</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>329691</t>
+          <t>326429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>281015</t>
+          <t>282437</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>343879</t>
+          <t>344326</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>564031</t>
+          <t>565437</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>651125</t>
+          <t>652634</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34641</t>
+          <t>35324</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63055</t>
+          <t>63163</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76852</t>
+          <t>73760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115427</t>
+          <t>114506</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119570</t>
+          <t>121035</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>166716</t>
+          <t>165718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>427160</t>
+          <t>426255</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>463364</t>
+          <t>463153</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>338017</t>
+          <t>336290</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>377291</t>
+          <t>374368</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>773703</t>
+          <t>775699</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>828428</t>
+          <t>830615</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76409</t>
+          <t>75766</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110375</t>
+          <t>111201</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72939</t>
+          <t>73490</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108104</t>
+          <t>107208</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159151</t>
+          <t>157647</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>211332</t>
+          <t>208338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>15950</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20580</t>
+          <t>19710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41969</t>
+          <t>41559</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27823</t>
+          <t>26952</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52879</t>
+          <t>52956</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2514451</t>
+          <t>2509516</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2606516</t>
+          <t>2606784</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2456402</t>
+          <t>2455923</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2556986</t>
+          <t>2556397</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4996877</t>
+          <t>4998598</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5135074</t>
+          <t>5138122</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>569288</t>
+          <t>568350</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>655375</t>
+          <t>659665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>632750</t>
+          <t>632594</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720408</t>
+          <t>724066</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1225227</t>
+          <t>1228724</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1355834</t>
+          <t>1357246</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78417</t>
+          <t>77386</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>114871</t>
+          <t>115947</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>165081</t>
+          <t>164089</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>217956</t>
+          <t>216051</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>253691</t>
+          <t>253328</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>320738</t>
+          <t>316534</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2012</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2012 (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>814169</t>
+          <t>816932</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>861072</t>
+          <t>862535</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1101329</t>
+          <t>1099141</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1152819</t>
+          <t>1156055</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1932677</t>
+          <t>1929078</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2002933</t>
+          <t>2000402</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,66%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89813</t>
+          <t>87809</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132688</t>
+          <t>130414</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>148207</t>
+          <t>145878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>196608</t>
+          <t>197433</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>247869</t>
+          <t>250610</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>315156</t>
+          <t>318703</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14406</t>
+          <t>15037</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33504</t>
+          <t>34245</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25196</t>
+          <t>24832</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50632</t>
+          <t>50866</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45671</t>
+          <t>46343</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76799</t>
+          <t>76734</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1609299</t>
+          <t>1603444</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1672226</t>
+          <t>1671576</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1404198</t>
+          <t>1401966</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1469646</t>
+          <t>1468834</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3025797</t>
+          <t>3031033</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3123028</t>
+          <t>3120659</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>236684</t>
+          <t>235161</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>299012</t>
+          <t>300398</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>210516</t>
+          <t>208775</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>267783</t>
+          <t>269129</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>464525</t>
+          <t>467287</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>548861</t>
+          <t>551515</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36153</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64730</t>
+          <t>63906</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,82 +3485,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>73572</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>57529</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>94190</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>122472</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>99895</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>148191</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>3,31%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>73572</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>57361</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>92546</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>122472</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>101445</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>145982</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>390822</t>
+          <t>391505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>425087</t>
+          <t>425859</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>366507</t>
+          <t>365741</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>400875</t>
+          <t>400661</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>770150</t>
+          <t>771950</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>816974</t>
+          <t>818004</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43466</t>
+          <t>43133</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75805</t>
+          <t>74511</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46442</t>
+          <t>44847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77155</t>
+          <t>76683</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97339</t>
+          <t>98418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140739</t>
+          <t>140253</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22885</t>
+          <t>22413</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21259</t>
+          <t>21146</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17794</t>
+          <t>17629</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37672</t>
+          <t>38647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2845145</t>
+          <t>2847831</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2931194</t>
+          <t>2930888</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2899486</t>
+          <t>2901756</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2993174</t>
+          <t>2995902</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5767115</t>
+          <t>5773901</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5905154</t>
+          <t>5900649</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>396422</t>
+          <t>393639</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>475522</t>
+          <t>476421</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>428999</t>
+          <t>428694</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>515160</t>
+          <t>513033</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>844284</t>
+          <t>846880</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>971330</t>
+          <t>964030</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>68901</t>
+          <t>68193</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>105445</t>
+          <t>105847</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>101108</t>
+          <t>101703</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>147103</t>
+          <t>146758</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>181627</t>
+          <t>179664</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>240134</t>
+          <t>242465</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2016</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>629970</t>
+          <t>629913</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>668036</t>
+          <t>667391</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>822625</t>
+          <t>823444</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>870500</t>
+          <t>870297</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1468530</t>
+          <t>1467416</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1528150</t>
+          <t>1528491</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,72%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66529</t>
+          <t>66501</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101012</t>
+          <t>100380</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93873</t>
+          <t>95082</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136803</t>
+          <t>137967</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>169776</t>
+          <t>171138</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>223876</t>
+          <t>223307</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13185</t>
+          <t>13344</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31450</t>
+          <t>31560</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>17260</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39430</t>
+          <t>39692</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34464</t>
+          <t>34688</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63638</t>
+          <t>64101</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1800001</t>
+          <t>1801680</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1858894</t>
+          <t>1860965</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1687900</t>
+          <t>1688732</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1748993</t>
+          <t>1750093</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3496330</t>
+          <t>3508730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3592209</t>
+          <t>3592319</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>163078</t>
+          <t>165626</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>220470</t>
+          <t>218226</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>177708</t>
+          <t>175822</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>229755</t>
+          <t>231036</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>357842</t>
+          <t>357665</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>437889</t>
+          <t>430874</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33457</t>
+          <t>34395</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62600</t>
+          <t>64087</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48094</t>
+          <t>48924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81052</t>
+          <t>79146</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89479</t>
+          <t>89159</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132292</t>
+          <t>132454</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>451365</t>
+          <t>450147</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>484490</t>
+          <t>484917</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>448385</t>
+          <t>448165</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>480913</t>
+          <t>481211</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>907689</t>
+          <t>910806</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>957826</t>
+          <t>956463</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,78%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49985</t>
+          <t>49248</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81000</t>
+          <t>81958</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47736</t>
+          <t>48234</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77893</t>
+          <t>77315</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106698</t>
+          <t>106900</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151877</t>
+          <t>150088</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22106</t>
+          <t>22059</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>9417</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26396</t>
+          <t>27156</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19049</t>
+          <t>19307</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41656</t>
+          <t>41324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2913256</t>
+          <t>2910107</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2991211</t>
+          <t>2987294</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2990609</t>
+          <t>2991526</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3073216</t>
+          <t>3072930</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5921532</t>
+          <t>5930643</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6041295</t>
+          <t>6039355</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,72%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>300888</t>
+          <t>302585</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>372035</t>
+          <t>375108</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>342124</t>
+          <t>339269</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>420074</t>
+          <t>413363</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>663773</t>
+          <t>664833</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>766315</t>
+          <t>762818</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63981</t>
+          <t>61811</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99115</t>
+          <t>100319</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>87403</t>
+          <t>85543</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>128559</t>
+          <t>127262</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>158450</t>
+          <t>157895</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>215023</t>
+          <t>215005</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2023</t>
+          <t>Población según si en el barrio donde vive sufre malos olores que llegan a su vivienda en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>439657</t>
+          <t>438961</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>467112</t>
+          <t>467912</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>657099</t>
+          <t>656962</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>683602</t>
+          <t>684064</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1104160</t>
+          <t>1104467</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1144078</t>
+          <t>1144344</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,3%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24864</t>
+          <t>24946</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46131</t>
+          <t>45694</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50317</t>
+          <t>50127</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73807</t>
+          <t>74298</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80134</t>
+          <t>80730</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112583</t>
+          <t>112254</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>16826</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36108</t>
+          <t>35079</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14568</t>
+          <t>14211</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29706</t>
+          <t>29713</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35970</t>
+          <t>35142</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59807</t>
+          <t>60824</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -7349,17 +7349,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2116531</t>
+          <t>2116532</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2078090</t>
+          <t>2080248</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2169601</t>
+          <t>2164895</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2015494</t>
+          <t>2015775</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2099193</t>
+          <t>2098877</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4114613</t>
+          <t>4111392</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4245309</t>
+          <t>4239478</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,66%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97215</t>
+          <t>104171</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>175461</t>
+          <t>174013</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>110511</t>
+          <t>108386</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>179963</t>
+          <t>179258</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>228904</t>
+          <t>231409</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>335783</t>
+          <t>336526</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17638</t>
+          <t>17125</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47627</t>
+          <t>46026</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25201</t>
+          <t>25495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51111</t>
+          <t>51585</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49336</t>
+          <t>50694</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91579</t>
+          <t>88614</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2289216</t>
+          <t>2289217</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2289216</t>
+          <t>2289217</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2289216</t>
+          <t>2289217</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>574408</t>
+          <t>574755</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>604360</t>
+          <t>604297</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>574451</t>
+          <t>574579</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>602841</t>
+          <t>603189</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1161279</t>
+          <t>1159929</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1201199</t>
+          <t>1199988</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31468</t>
+          <t>31485</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57920</t>
+          <t>57658</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40729</t>
+          <t>41397</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65159</t>
+          <t>66199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77930</t>
+          <t>78785</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113706</t>
+          <t>113138</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6323</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23994</t>
+          <t>21720</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11254</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25223</t>
+          <t>24757</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19677</t>
+          <t>20310</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42205</t>
+          <t>44495</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3118880</t>
+          <t>3120114</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3226047</t>
+          <t>3232019</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3271848</t>
+          <t>3271249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3369232</t>
+          <t>3370606</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6409341</t>
+          <t>6405077</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6561030</t>
+          <t>6559351</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>169214</t>
+          <t>169276</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>253843</t>
+          <t>255952</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211021</t>
+          <t>215771</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>295569</t>
+          <t>296269</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>412022</t>
+          <t>407905</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>539005</t>
+          <t>538125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48622</t>
+          <t>48972</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90244</t>
+          <t>90143</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>59130</t>
+          <t>59846</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>95045</t>
+          <t>96057</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>120108</t>
+          <t>118742</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>175381</t>
+          <t>174333</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A02-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05A02-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>740097</t>
+          <t>738391</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>796098</t>
+          <t>793641</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>937406</t>
+          <t>939119</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1002398</t>
+          <t>1001727</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1701601</t>
+          <t>1697623</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1785547</t>
+          <t>1784756</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>198344</t>
+          <t>200532</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>250922</t>
+          <t>251779</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>248972</t>
+          <t>249099</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>306795</t>
+          <t>306792</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>458074</t>
+          <t>458008</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>537225</t>
+          <t>536842</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28499</t>
+          <t>28432</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54179</t>
+          <t>52180</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>50720</t>
+          <t>50896</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>81975</t>
+          <t>82696</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>85677</t>
+          <t>87101</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>124015</t>
+          <t>123587</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1313632</t>
+          <t>1312115</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1378955</t>
+          <t>1376350</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1142538</t>
+          <t>1142899</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1210186</t>
+          <t>1214375</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2473273</t>
+          <t>2471751</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2569139</t>
+          <t>2565423</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,39%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>265809</t>
+          <t>268016</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>326429</t>
+          <t>328498</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>282437</t>
+          <t>280208</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>344326</t>
+          <t>345105</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>565437</t>
+          <t>566251</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>652634</t>
+          <t>651892</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35324</t>
+          <t>33788</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63163</t>
+          <t>61935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73760</t>
+          <t>77574</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114506</t>
+          <t>114956</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121035</t>
+          <t>117382</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>165718</t>
+          <t>166562</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>426255</t>
+          <t>425243</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>463153</t>
+          <t>462556</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>336290</t>
+          <t>337151</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>374368</t>
+          <t>375907</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>775699</t>
+          <t>772621</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>830615</t>
+          <t>826767</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,78%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75766</t>
+          <t>76866</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111201</t>
+          <t>113173</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107208</t>
+          <t>108268</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157647</t>
+          <t>160095</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208338</t>
+          <t>209231</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15950</t>
+          <t>16732</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19710</t>
+          <t>19527</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41559</t>
+          <t>41394</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26952</t>
+          <t>27521</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52956</t>
+          <t>53574</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2509516</t>
+          <t>2511051</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2606784</t>
+          <t>2605799</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2455923</t>
+          <t>2454741</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2556397</t>
+          <t>2558527</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4998598</t>
+          <t>4998356</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5138122</t>
+          <t>5135256</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>568350</t>
+          <t>569910</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>659665</t>
+          <t>659460</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>632594</t>
+          <t>632194</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>724066</t>
+          <t>725107</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1228724</t>
+          <t>1233066</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1357246</t>
+          <t>1353572</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77386</t>
+          <t>78243</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115947</t>
+          <t>115575</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164089</t>
+          <t>163632</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>216051</t>
+          <t>220142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>253328</t>
+          <t>253797</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>316534</t>
+          <t>318891</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>816932</t>
+          <t>816468</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>862535</t>
+          <t>861786</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1099141</t>
+          <t>1101649</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1156055</t>
+          <t>1156412</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1929078</t>
+          <t>1930933</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2000402</t>
+          <t>2002888</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87809</t>
+          <t>90612</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130414</t>
+          <t>131000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>145878</t>
+          <t>144662</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>197433</t>
+          <t>196531</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>250610</t>
+          <t>249613</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>318703</t>
+          <t>315452</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15037</t>
+          <t>15668</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34245</t>
+          <t>35035</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24832</t>
+          <t>25138</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50866</t>
+          <t>50292</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>46343</t>
+          <t>46886</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76734</t>
+          <t>77431</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1603444</t>
+          <t>1605454</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1671576</t>
+          <t>1671836</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1401966</t>
+          <t>1404624</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1468834</t>
+          <t>1470401</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3031033</t>
+          <t>3030815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3120659</t>
+          <t>3124001</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,31%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>235161</t>
+          <t>236022</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>300398</t>
+          <t>298571</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>208775</t>
+          <t>207689</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>269129</t>
+          <t>269044</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>467287</t>
+          <t>461126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>551515</t>
+          <t>547641</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35934</t>
+          <t>36451</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63906</t>
+          <t>65206</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57529</t>
+          <t>57405</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94190</t>
+          <t>93561</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99895</t>
+          <t>100440</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>148191</t>
+          <t>149873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>391505</t>
+          <t>390769</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>425859</t>
+          <t>424312</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>365741</t>
+          <t>366803</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>400661</t>
+          <t>400641</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>771950</t>
+          <t>766650</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>818004</t>
+          <t>815423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43133</t>
+          <t>44940</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74511</t>
+          <t>75335</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44847</t>
+          <t>45560</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76683</t>
+          <t>76972</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98418</t>
+          <t>98599</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140253</t>
+          <t>143154</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22413</t>
+          <t>23249</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21146</t>
+          <t>20936</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17629</t>
+          <t>17544</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>38647</t>
+          <t>37968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2847831</t>
+          <t>2844306</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2930888</t>
+          <t>2930981</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2901756</t>
+          <t>2900893</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2995902</t>
+          <t>2997149</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5773901</t>
+          <t>5782642</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5900649</t>
+          <t>5902827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,9%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>393639</t>
+          <t>394736</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>476421</t>
+          <t>476171</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>428694</t>
+          <t>427441</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>513033</t>
+          <t>513872</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>846880</t>
+          <t>850120</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>964030</t>
+          <t>957142</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>68193</t>
+          <t>68434</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>105847</t>
+          <t>106265</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>101703</t>
+          <t>102206</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>146758</t>
+          <t>147499</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>179664</t>
+          <t>183455</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>242465</t>
+          <t>241642</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>629913</t>
+          <t>630864</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>667391</t>
+          <t>667855</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>823444</t>
+          <t>824602</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>870297</t>
+          <t>870130</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1467416</t>
+          <t>1471159</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1528491</t>
+          <t>1528942</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66501</t>
+          <t>65451</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100380</t>
+          <t>99552</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95082</t>
+          <t>95051</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137967</t>
+          <t>137675</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171138</t>
+          <t>170507</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>223307</t>
+          <t>222475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13344</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31560</t>
+          <t>31493</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>17322</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39692</t>
+          <t>40048</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34688</t>
+          <t>34162</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64101</t>
+          <t>62316</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1801680</t>
+          <t>1804116</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1860965</t>
+          <t>1860855</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1688732</t>
+          <t>1689869</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1750093</t>
+          <t>1748656</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3508730</t>
+          <t>3510046</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3592319</t>
+          <t>3595799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,73%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>165626</t>
+          <t>164398</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>218226</t>
+          <t>217602</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>175822</t>
+          <t>174980</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>231036</t>
+          <t>228699</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>357665</t>
+          <t>357274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>430874</t>
+          <t>431215</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34395</t>
+          <t>32585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64087</t>
+          <t>60931</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48924</t>
+          <t>46745</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79146</t>
+          <t>78083</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89159</t>
+          <t>87608</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132454</t>
+          <t>131167</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>450147</t>
+          <t>450416</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>484917</t>
+          <t>485785</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>448165</t>
+          <t>445982</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>481211</t>
+          <t>481286</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>910806</t>
+          <t>909405</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>956463</t>
+          <t>956843</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49248</t>
+          <t>50239</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81958</t>
+          <t>80659</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48234</t>
+          <t>47369</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77315</t>
+          <t>78884</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106900</t>
+          <t>104662</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150088</t>
+          <t>149909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22059</t>
+          <t>23059</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27156</t>
+          <t>27733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19307</t>
+          <t>19470</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41324</t>
+          <t>41756</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2910107</t>
+          <t>2910368</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2987294</t>
+          <t>2986181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2991526</t>
+          <t>2990259</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3072930</t>
+          <t>3072863</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5930643</t>
+          <t>5926559</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6039355</t>
+          <t>6042067</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,76%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>302585</t>
+          <t>303767</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>375108</t>
+          <t>373408</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>339269</t>
+          <t>342146</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>413363</t>
+          <t>413741</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>664833</t>
+          <t>665187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>762818</t>
+          <t>762581</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61811</t>
+          <t>62416</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100319</t>
+          <t>99756</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>85543</t>
+          <t>85929</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>127262</t>
+          <t>127830</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>157895</t>
+          <t>158472</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>215005</t>
+          <t>214140</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>454554</t>
+          <t>510022</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>438961</t>
+          <t>494778</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>467912</t>
+          <t>524250</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>671130</t>
+          <t>730924</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>656962</t>
+          <t>715487</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>684064</t>
+          <t>744839</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1125684</t>
+          <t>1240945</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1104467</t>
+          <t>1218463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1144344</t>
+          <t>1262172</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,26%</t>
         </is>
       </c>
     </row>
@@ -7006,102 +7006,102 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34239</t>
+          <t>41041</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24946</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45694</t>
+          <t>53438</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>9,25%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>66438</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>54842</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>81767</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>107479</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>90092</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>124324</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>8,89%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60976</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>50127</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>74298</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>8,09%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>9,86%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>95215</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>80730</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>112254</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>7,51%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25126</t>
+          <t>26381</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16826</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35079</t>
+          <t>38048</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21216</t>
+          <t>23569</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14211</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29713</t>
+          <t>33400</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>46342</t>
+          <t>49951</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35142</t>
+          <t>38120</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>60824</t>
+          <t>64207</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>513919</t>
+          <t>577444</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>513919</t>
+          <t>577444</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>513919</t>
+          <t>577444</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>753322</t>
+          <t>820931</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>753322</t>
+          <t>820931</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>753322</t>
+          <t>820931</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1267241</t>
+          <t>1398374</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1267241</t>
+          <t>1398374</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1267241</t>
+          <t>1398374</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2116532</t>
+          <t>2041655</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2080248</t>
+          <t>2010793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2164895</t>
+          <t>2068706</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2051572</t>
+          <t>1953723</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2015775</t>
+          <t>1924282</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2098877</t>
+          <t>1979645</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4168104</t>
+          <t>3995377</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4111392</t>
+          <t>3949959</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4239478</t>
+          <t>4029701</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>142430</t>
+          <t>155771</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>104171</t>
+          <t>131106</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>174013</t>
+          <t>185654</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>147918</t>
+          <t>176049</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>108386</t>
+          <t>152396</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>179258</t>
+          <t>204765</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>290348</t>
+          <t>331821</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>231409</t>
+          <t>301310</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>336526</t>
+          <t>371989</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30255</t>
+          <t>31955</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17125</t>
+          <t>21248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46026</t>
+          <t>47461</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37751</t>
+          <t>40929</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25495</t>
+          <t>30593</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51585</t>
+          <t>53218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>68006</t>
+          <t>72884</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50694</t>
+          <t>56261</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88614</t>
+          <t>91333</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2289217</t>
+          <t>2229381</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2289217</t>
+          <t>2229381</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2289217</t>
+          <t>2229381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2237240</t>
+          <t>2170702</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2237240</t>
+          <t>2170702</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2237240</t>
+          <t>2170702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4526457</t>
+          <t>4400082</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4526457</t>
+          <t>4400082</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4526457</t>
+          <t>4400082</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>591325</t>
+          <t>649094</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>574755</t>
+          <t>631450</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>604297</t>
+          <t>664727</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>589881</t>
+          <t>651239</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>574579</t>
+          <t>634065</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>603189</t>
+          <t>664730</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1181207</t>
+          <t>1300334</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1159929</t>
+          <t>1275622</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1199988</t>
+          <t>1322315</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,54%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42823</t>
+          <t>49077</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31485</t>
+          <t>35722</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57658</t>
+          <t>65488</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>51831</t>
+          <t>61969</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41397</t>
+          <t>50187</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66199</t>
+          <t>77172</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>94654</t>
+          <t>111046</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78785</t>
+          <t>91149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113138</t>
+          <t>132393</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12475</t>
+          <t>13415</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21720</t>
+          <t>24152</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16972</t>
+          <t>19782</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10351</t>
+          <t>13061</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24757</t>
+          <t>29179</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,22 +8101,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>29446</t>
+          <t>33197</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20310</t>
+          <t>22480</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44495</t>
+          <t>47111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>658684</t>
+          <t>732990</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>658684</t>
+          <t>732990</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>658684</t>
+          <t>732990</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1305308</t>
+          <t>1444577</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1305308</t>
+          <t>1444577</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1305308</t>
+          <t>1444577</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3162410</t>
+          <t>3200770</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3120114</t>
+          <t>3157873</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3232019</t>
+          <t>3234817</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3312584</t>
+          <t>3335886</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3271249</t>
+          <t>3297876</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3370606</t>
+          <t>3370130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6474994</t>
+          <t>6536655</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6405077</t>
+          <t>6484636</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6559351</t>
+          <t>6580819</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>219493</t>
+          <t>245889</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>169276</t>
+          <t>214542</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>255952</t>
+          <t>281035</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>260724</t>
+          <t>304456</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>215771</t>
+          <t>273930</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>296269</t>
+          <t>338870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>480217</t>
+          <t>550345</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>407905</t>
+          <t>506902</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>538125</t>
+          <t>599348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67856</t>
+          <t>71752</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48972</t>
+          <t>55753</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90143</t>
+          <t>93936</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>75938</t>
+          <t>84280</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>59846</t>
+          <t>69421</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>96057</t>
+          <t>102063</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>143794</t>
+          <t>156032</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>118742</t>
+          <t>133026</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>174333</t>
+          <t>182346</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3449759</t>
+          <t>3518411</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3449759</t>
+          <t>3518411</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3449759</t>
+          <t>3518411</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3649247</t>
+          <t>3724622</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3649247</t>
+          <t>3724622</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3649247</t>
+          <t>3724622</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7099005</t>
+          <t>7243033</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7099005</t>
+          <t>7243033</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7099005</t>
+          <t>7243033</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
